--- a/data/google_news_dedup_audit_10_0426_UTC.xlsx
+++ b/data/google_news_dedup_audit_10_0426_UTC.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,10 +448,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>0.694036602973938</v>
+        <v>0.7585928440093994</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -460,250 +460,250 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Amazon to stock Lilly's new weight-loss pill at US kiosks, offer same-day delivery - Reuters</t>
+          <t>Amazon Pharmacy to offer Eli Lilly’s Foundayo via same-day delivery - Yahoo Finance</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8620768785476685</v>
+        <v>0.7299765348434448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Amazon Pharmacy and Eli Lilly Launch Foundayo GLP-1 with Same-Day Delivery and Transparent Pricing - HLTH</t>
+          <t>Shipping traffic around Antwerp port partially halted after oil spill - Reuters</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Amazon Pharmacy to Offer Eli Lilly and Company’s New GLP-1 Pill Foundayo via Same-Day Delivery - Business Wire</t>
+          <t>Bunker Spill Closes Port of Antwerp to River Traffic - Ship &amp; Bunker</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7195770740509033</v>
+        <v>0.8377208709716797</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Amazon Pharmacy and Eli Lilly Launch Foundayo GLP-1 with Same-Day Delivery and Transparent Pricing - HLTH</t>
+          <t>Shipping traffic around Antwerp port partially halted after oil spill - Reuters</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Amazon Pharmacy adds same-day delivery for Eli Lilly's Foundayo weight-loss pill - qz.com</t>
+          <t>Oil spill snarls shipping traffic in Antwerp port - Northeast Mississippi Daily Journal</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7854079604148865</v>
+        <v>0.8478007912635803</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Amazon Pharmacy and Eli Lilly Launch Foundayo GLP-1 with Same-Day Delivery and Transparent Pricing - HLTH</t>
+          <t>Shipping traffic around Antwerp port partially halted after oil spill - Reuters</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Amazon expands GLP-1 access with Lilly pill, fast delivery - irishsun.com</t>
+          <t>Belgian Port of Antwerp Is Blocked to Vessels Due to Oil Spill - Bloomberg.com</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6066931486129761</v>
+        <v>0.8569614291191101</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Amazon Pharmacy and Eli Lilly Launch Foundayo GLP-1 with Same-Day Delivery and Transparent Pricing - HLTH</t>
+          <t>Shipping traffic around Antwerp port partially halted after oil spill - Reuters</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Amazon to sell new weight-loss pill Foundayo via kiosks, home delivery - USA Today</t>
+          <t>Oil spill snarls shipping traffic in Antwerp port - The Killeen Daily Herald</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6650011539459229</v>
+        <v>0.7095199227333069</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Amazon Pharmacy and Eli Lilly Launch Foundayo GLP-1 with Same-Day Delivery and Transparent Pricing - HLTH</t>
+          <t>Shipping traffic around Antwerp port partially halted after oil spill - Reuters</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Amazon Offers Same-Day Delivery of Eli Lilly’s (LLY) Weight-Loss Pill - TipRanks</t>
+          <t>A container ship docked in Antwerp, where an oil spill has caused a near-shutdown of maritime traffic - themercury.com</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7666571140289307</v>
+        <v>0.885540246963501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Amazon Pharmacy and Eli Lilly Launch Foundayo GLP-1 with Same-Day Delivery and Transparent Pricing - HLTH</t>
+          <t>Shipping traffic around Antwerp port partially halted after oil spill - Reuters</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Amazon Just Brought Same-Day Delivery to GLP-1 Weight-Loss Drugs - inc.com</t>
+          <t>Oil spill snarls shipping traffic in Antwerp port - nbc39.com</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6648832559585571</v>
+        <v>0.8982028961181641</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Amazon Pharmacy and Eli Lilly Launch Foundayo GLP-1 with Same-Day Delivery and Transparent Pricing - HLTH</t>
+          <t>Shipping traffic around Antwerp port partially halted after oil spill - Reuters</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Amazon expands same-day delivery range of Eli Lilly weight loss drugs - Chain Store Age</t>
+          <t>Oil Spill Forces Partial Shipping Halt at Port of Antwerp - Marine Link</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8444110155105591</v>
+        <v>0.863633930683136</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Amazon Pharmacy and Eli Lilly Launch Foundayo GLP-1 with Same-Day Delivery and Transparent Pricing - HLTH</t>
+          <t>Shipping traffic around Antwerp port partially halted after oil spill - Reuters</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Amazon Pharmacy offers Eli Lilly’s GLP-1 pill Foundayo via Same-Day Delivery - Drug Store News</t>
+          <t>Oil spill snarls shipping traffic in Antwerp port - Community Newspaper Group</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5478382706642151</v>
+        <v>0.8132416009902954</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Amazon Pharmacy and Eli Lilly Launch Foundayo GLP-1 with Same-Day Delivery and Transparent Pricing - HLTH</t>
+          <t>Shipping traffic around Antwerp port partially halted after oil spill - Reuters</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Amazon expands access to weight-loss pill with kiosks, same-day delivery - fox61.com</t>
+          <t>Major oil spill halts operations at Belgium's Port of Antwerp - Anadolu Ajansı</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8386764526367188</v>
+        <v>0.8642263412475586</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Amazon (AMZN) Stock Surges on Eli Lilly Weight-Loss Drug Partnership - MEXC</t>
+          <t>Shipping traffic around Antwerp port partially halted after oil spill - Reuters</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Amazon (AMZN) Stock Jumps After Landing Eli Lilly’s Hot Weight-Loss Pill - MEXC</t>
+          <t>Oil spill snarls shipping traffic in Antwerp port - Iosco County News Herald</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7680839896202087</v>
+        <v>0.7163055539131165</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Amazon contractors clash with Teamsters at raucous NYC Council hearing on controversial delivery legislation - New York Post</t>
+          <t>Shipping traffic around Antwerp port partially halted after oil spill - Reuters</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Amazon Teamsters Urge Passage of Delivery Protection Act in NYC Council Hearing - International Brotherhood of Teamsters</t>
+          <t>Oil Spill Shuts Key Access to Antwerp Port, Cleanup Under Way - gCaptain</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="B14" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7299765348434448</v>
+        <v>0.8455726504325867</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -712,19 +712,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bunker Spill Closes Port of Antwerp to River Traffic - Ship &amp; Bunker</t>
+          <t>Belgium’s Antwerp port hit by oil spill, operations halted - News.az</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="B15" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8377208709716797</v>
+        <v>0.8104636073112488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -733,19 +733,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oil spill snarls shipping traffic in Antwerp port - Northeast Mississippi Daily Journal</t>
+          <t>Oil spill brings Port of Antwerp traffic to a halt - belganewsagency.eu</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="B16" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8569614291191101</v>
+        <v>0.8411275744438171</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -754,19 +754,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oil spill snarls shipping traffic in Antwerp port - The Killeen Daily Herald</t>
+          <t>Oil spill snarls shipping traffic in Antwerp port - The Elkhart Truth</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="B17" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8404213190078735</v>
+        <v>0.791996955871582</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -775,19 +775,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Oil spill snarls shipping traffic in Antwerp port - DerbyInformer.com</t>
+          <t>Oil spill triggers major disruption at Port of Antwerp-Bruges - WorldCargo News</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="B18" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C18" t="n">
-        <v>0.863633930683136</v>
+        <v>0.972278356552124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -796,511 +796,175 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oil spill snarls shipping traffic in Antwerp port - Community Newspaper Group</t>
+          <t>Shipping traffic around Antwerp port partially halted after oil spill - TradingView</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8642263412475586</v>
+        <v>0.604670524597168</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Shipping traffic around Antwerp port partially halted after oil spill - Reuters</t>
+          <t>Watch: Traffic chaos across Ireland as fuel protest convoys hit major routes - MSN</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oil spill snarls shipping traffic in Antwerp port - Iosco County News Herald</t>
+          <t>Protester says they are willing to close Ireland down over fuel costs - BBC</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B20" t="n">
         <v>42</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7163055539131165</v>
+        <v>0.6343472003936768</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Shipping traffic around Antwerp port partially halted after oil spill - Reuters</t>
+          <t>Watch: Traffic chaos across Ireland as fuel protest convoys hit major routes - MSN</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oil Spill Shuts Key Access to Antwerp Port, Cleanup Under Way - gCaptain</t>
+          <t>Irish fuel protests enter fourth day as government seeks to head off shortages, open blocked roads - NBC News</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B21" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8104636073112488</v>
+        <v>0.763576865196228</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Shipping traffic around Antwerp port partially halted after oil spill - Reuters</t>
+          <t>Watch: Traffic chaos across Ireland as fuel protest convoys hit major routes - MSN</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Oil spill brings Port of Antwerp traffic to a halt - belganewsagency.eu</t>
+          <t>Where are the fuel protests on Friday and which roads are impacted in Dublin and across Ireland? - The Irish Times</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B22" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8531131148338318</v>
+        <v>0.7678929567337036</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Shipping traffic around Antwerp port partially halted after oil spill - Reuters</t>
+          <t>Watch: Traffic chaos across Ireland as fuel protest convoys hit major routes - MSN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oil spill snarls shipping traffic in Antwerp port - swiowanewssource.com</t>
+          <t>Irish fuel protests: People walk along motorway towards Dublin Airport as blockade continues - AOL.com</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="B23" t="n">
         <v>51</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8411275744438171</v>
+        <v>0.8787754774093628</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Shipping traffic around Antwerp port partially halted after oil spill - Reuters</t>
+          <t>Lunedì consiglio federale Lega a Milano, fari sulla "manifestazione dei Patrioti" - il Nord Est</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oil spill snarls shipping traffic in Antwerp port - The Elkhart Truth</t>
+          <t>Lunedì consiglio federale Lega a Milano, fari sulla "manifestazione dei Patrioti" - Espansione TV</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="B24" t="n">
         <v>52</v>
       </c>
       <c r="C24" t="n">
-        <v>0.791996955871582</v>
+        <v>0.9493935704231262</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Shipping traffic around Antwerp port partially halted after oil spill - Reuters</t>
+          <t>Lunedì consiglio federale Lega a Milano, fari sulla "manifestazione dei Patrioti" - il Nord Est</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oil spill triggers major disruption at Port of Antwerp-Bruges - WorldCargo News</t>
+          <t>Lunedì consiglio federale Lega a Milano, fari sulla "manifestazione dei Patrioti" - Bresciaoggi</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="B25" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C25" t="n">
-        <v>0.972278356552124</v>
+        <v>0.9383876919746399</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Shipping traffic around Antwerp port partially halted after oil spill - Reuters</t>
+          <t>Lunedì consiglio federale Lega a Milano, fari sulla "manifestazione dei Patrioti" - il Nord Est</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shipping traffic around Antwerp port partially halted after oil spill - TradingView</t>
+          <t>Lunedì consiglio federale Lega a Milano, fari sulla "manifestazione dei Patrioti" - Giornale di Brescia</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="B26" t="n">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8417156934738159</v>
+        <v>0.6643757820129395</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Suffolk County police rescue teen stuck in mud at Wertheim National Wildlife Refuge - AOL.com</t>
+          <t>Lunedì consiglio federale Lega a Milano, fari sulla "manifestazione dei Patrioti" - il Nord Est</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Copter Rescues Teen Stuck In Mud At Wertheim National Refuge - MSN</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>78</v>
-      </c>
-      <c r="B27" t="n">
-        <v>81</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0.7477620840072632</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Protester says they are willing to close Ireland down over fuel costs - BBC</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>What’s behind Ireland’s fuel protests and why they’re escalating - The Independent</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>78</v>
-      </c>
-      <c r="B28" t="n">
-        <v>84</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.6698101758956909</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Protester says they are willing to close Ireland down over fuel costs - BBC</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Third day of fuel price protests bring Dublin to a standstill | ITV News - ITVX</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>78</v>
-      </c>
-      <c r="B29" t="n">
-        <v>89</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.6986497044563293</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Protester says they are willing to close Ireland down over fuel costs - BBC</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Irish fuel protests: People walk along motorway towards Dublin Airport as blockade continues - AOL.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>78</v>
-      </c>
-      <c r="B30" t="n">
-        <v>90</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0.7573920488357544</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Protester says they are willing to close Ireland down over fuel costs - BBC</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Fuel price protesters say they will continue blockades despite claiming to have secured meeting - The Irish Times</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>78</v>
-      </c>
-      <c r="B31" t="n">
-        <v>92</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0.5410337448120117</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Protester says they are willing to close Ireland down over fuel costs - BBC</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>What is behind the fuel protests? - BreakingNews.ie</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>78</v>
-      </c>
-      <c r="B32" t="n">
-        <v>93</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0.7147884368896484</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Protester says they are willing to close Ireland down over fuel costs - BBC</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Where are the fuel protests on Friday and which roads are impacted in Dublin and across Ireland? - The Irish Times</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>88</v>
-      </c>
-      <c r="B33" t="n">
-        <v>91</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0.9174472093582153</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>‘Panic buying’ setting in on fourth day of fuel protest - East London Advertiser</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>‘Panic buying’ setting in on fourth day of fuel protest - London Now</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>95</v>
-      </c>
-      <c r="B34" t="n">
-        <v>96</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0.6472791433334351</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Italian Air Traffic Controllers Set for 4-Hour National Strike on 10 April—Hundreds of Flights Already Cancelled - VisaHQ</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Italy Faces Major Air Traffic Disruption as National Strike Hits Key Airports and Flights: Everything You Need to Know - Travel And Tour World</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>95</v>
-      </c>
-      <c r="B35" t="n">
-        <v>99</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0.7240470051765442</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Italian Air Traffic Controllers Set for 4-Hour National Strike on 10 April—Hundreds of Flights Already Cancelled - VisaHQ</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Italy Aviation Strike to Disrupt Rome and Milan Flights - thetraveler.org</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>95</v>
-      </c>
-      <c r="B36" t="n">
-        <v>100</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0.6436511278152466</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Italian Air Traffic Controllers Set for 4-Hour National Strike on 10 April—Hundreds of Flights Already Cancelled - VisaHQ</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Flight disruptions ahead with Italy's aviation strikes scheduled to start today - RSVP Live</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>95</v>
-      </c>
-      <c r="B37" t="n">
-        <v>101</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0.6583847999572754</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Italian Air Traffic Controllers Set for 4-Hour National Strike on 10 April—Hundreds of Flights Already Cancelled - VisaHQ</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Italy April Aviation Strike: Rome and Milan Flight Disruptions on 10 April 2026 - Nomad Lawyer</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>95</v>
-      </c>
-      <c r="B38" t="n">
-        <v>103</v>
-      </c>
-      <c r="C38" t="n">
-        <v>0.7240470051765442</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Italian Air Traffic Controllers Set for 4-Hour National Strike on 10 April—Hundreds of Flights Already Cancelled - VisaHQ</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Italy aviation strike to disrupt Rome and Milan flights - thetraveler.org</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>104</v>
-      </c>
-      <c r="B39" t="n">
-        <v>106</v>
-      </c>
-      <c r="C39" t="n">
-        <v>0.8787754774093628</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Lunedì consiglio federale Lega a Milano, fari sulla "manifestazione dei Patrioti" - il Nord Est</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Lunedì consiglio federale Lega a Milano, fari sulla "manifestazione dei Patrioti" - Espansione TV</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>104</v>
-      </c>
-      <c r="B40" t="n">
-        <v>115</v>
-      </c>
-      <c r="C40" t="n">
-        <v>0.9383876919746399</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Lunedì consiglio federale Lega a Milano, fari sulla "manifestazione dei Patrioti" - il Nord Est</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Lunedì consiglio federale Lega a Milano, fari sulla "manifestazione dei Patrioti" - Giornale di Brescia</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>104</v>
-      </c>
-      <c r="B41" t="n">
-        <v>117</v>
-      </c>
-      <c r="C41" t="n">
-        <v>0.6643757820129395</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Lunedì consiglio federale Lega a Milano, fari sulla "manifestazione dei Patrioti" - il Nord Est</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
           <t>Consiglio Federale Lega a Milano: analisi strategica e scenari verso la manifestazione dei Patrioti - Mitico channel</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>113</v>
-      </c>
-      <c r="B42" t="n">
-        <v>118</v>
-      </c>
-      <c r="C42" t="n">
-        <v>0.7541981935501099</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Remigration Summit, Sala rassegnato: “Evento inappropriato, evoca deportazioni. Ma non si può evitare” - Il Giorno</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Scintille sul Remigration Summit del 18 aprile, Forza Italia: iniziativa razzista. Pd: facciano cadere governo allora - Il Giorno</t>
         </is>
       </c>
     </row>
